--- a/data/trans_dic/P16A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,23</t>
+          <t>4,05; 7,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,57</t>
+          <t>4,72; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,18</t>
+          <t>3,78; 7,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,56</t>
+          <t>8,11; 12,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,43</t>
+          <t>6,97; 11,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 18,8</t>
+          <t>13,18; 18,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,64</t>
+          <t>14,93; 20,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 19,08</t>
+          <t>12,91; 19,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,76</t>
+          <t>6,05; 8,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,0</t>
+          <t>9,56; 13,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 13,47</t>
+          <t>9,86; 13,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,37</t>
+          <t>11,85; 15,38</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,48</t>
+          <t>3,56; 6,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,69</t>
+          <t>5,34; 8,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,3</t>
+          <t>4,37; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,45</t>
+          <t>2,59; 7,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,6</t>
+          <t>9,54; 13,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,82</t>
+          <t>13,54; 18,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,88</t>
+          <t>11,42; 15,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 19,84</t>
+          <t>16,15; 20,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,48</t>
+          <t>7,08; 9,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,69</t>
+          <t>9,86; 12,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,1</t>
+          <t>8,34; 11,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,83</t>
+          <t>7,58; 12,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,0</t>
+          <t>2,8; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,47</t>
+          <t>3,79; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,25</t>
+          <t>4,63; 8,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,88</t>
+          <t>6,57; 10,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,7</t>
+          <t>9,92; 14,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,27; 17,72</t>
+          <t>12,38; 17,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 16,51</t>
+          <t>11,58; 16,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,53</t>
+          <t>5,86; 16,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,8</t>
+          <t>6,94; 9,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,86</t>
+          <t>8,68; 11,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,76</t>
+          <t>8,68; 12,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,67</t>
+          <t>7,08; 12,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,47</t>
+          <t>3,78; 6,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,59</t>
+          <t>5,97; 9,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,17</t>
+          <t>5,92; 9,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 12,12</t>
+          <t>8,34; 12,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 13,85</t>
+          <t>9,62; 13,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,29</t>
+          <t>13,88; 18,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 18,77</t>
+          <t>13,88; 18,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 20,12</t>
+          <t>14,7; 20,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 9,73</t>
+          <t>7,31; 9,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,62</t>
+          <t>10,65; 13,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 13,65</t>
+          <t>10,63; 13,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,81</t>
+          <t>12,34; 15,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,75</t>
+          <t>4,2; 5,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,62</t>
+          <t>5,79; 7,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,16</t>
+          <t>5,44; 7,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,39</t>
+          <t>6,43; 9,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,25</t>
+          <t>10,06; 12,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,42; 16,8</t>
+          <t>14,27; 16,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 16,45</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,89; 17,68</t>
+          <t>13,22; 17,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,85</t>
+          <t>7,51; 8,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,04</t>
+          <t>10,48; 12,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,57</t>
+          <t>10,08; 11,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 13,44</t>
+          <t>10,6; 13,41</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27095; 50157</t>
+          <t>28098; 50480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34296; 60269</t>
+          <t>33237; 61878</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25871; 48459</t>
+          <t>25517; 49620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51948; 79800</t>
+          <t>51505; 79436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50125; 78703</t>
+          <t>47995; 79342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92039; 131037</t>
+          <t>91859; 130299</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98370; 138841</t>
+          <t>100436; 140572</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97337; 138420</t>
+          <t>93605; 138105</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83553; 121133</t>
+          <t>83681; 120295</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134091; 182013</t>
+          <t>133930; 183057</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133329; 181585</t>
+          <t>132917; 180418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>158261; 209136</t>
+          <t>161238; 209322</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33565; 62366</t>
+          <t>34229; 61882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55208; 88451</t>
+          <t>54315; 88643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45513; 74595</t>
+          <t>44665; 75302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35755; 88863</t>
+          <t>30901; 87876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93166; 131686</t>
+          <t>92432; 130682</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>137523; 183914</t>
+          <t>139743; 187389</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120097; 165606</t>
+          <t>119141; 163171</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>153685; 190183</t>
+          <t>154800; 192396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135226; 183034</t>
+          <t>136699; 185508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203402; 260075</t>
+          <t>202198; 262658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174183; 229323</t>
+          <t>172348; 227288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>161421; 276029</t>
+          <t>163053; 275307</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19584; 40730</t>
+          <t>18967; 40664</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27669; 56621</t>
+          <t>28724; 57673</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35252; 62643</t>
+          <t>35151; 63064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46880; 76704</t>
+          <t>46327; 75528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67906; 100544</t>
+          <t>67813; 100056</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95322; 137725</t>
+          <t>96179; 138278</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89007; 129580</t>
+          <t>90912; 131827</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62508; 154319</t>
+          <t>54709; 154129</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>95293; 133471</t>
+          <t>94501; 133926</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133066; 182083</t>
+          <t>133275; 183822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133881; 181648</t>
+          <t>134000; 185287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119392; 207552</t>
+          <t>116034; 209691</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36472; 60928</t>
+          <t>35621; 60884</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56157; 90881</t>
+          <t>56626; 91536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55271; 85942</t>
+          <t>55541; 87295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78176; 112352</t>
+          <t>77277; 112760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100908; 143848</t>
+          <t>99944; 141073</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143412; 192384</t>
+          <t>145993; 193792</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>144262; 195927</t>
+          <t>144876; 193568</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>157979; 220299</t>
+          <t>160904; 222538</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>143743; 192657</t>
+          <t>144754; 194276</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212053; 272313</t>
+          <t>212931; 275850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>209564; 270384</t>
+          <t>210591; 271030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>252021; 319635</t>
+          <t>249431; 320066</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>137978; 188322</t>
+          <t>137711; 186644</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>198997; 261076</t>
+          <t>198349; 262165</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187163; 243107</t>
+          <t>184534; 240749</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225782; 324905</t>
+          <t>222400; 320799</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>341295; 413853</t>
+          <t>339971; 408540</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>513093; 597912</t>
+          <t>507726; 595880</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>495516; 583035</t>
+          <t>494082; 583729</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>478497; 656282</t>
+          <t>490632; 660644</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>495709; 588787</t>
+          <t>499543; 582131</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>728374; 840686</t>
+          <t>732170; 840872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>696759; 802928</t>
+          <t>699388; 800588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>775592; 964118</t>
+          <t>760517; 961645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,27</t>
+          <t>3,92; 7,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,8</t>
+          <t>4,82; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,35</t>
+          <t>3,78; 7,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,5</t>
+          <t>8,15; 12,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,53</t>
+          <t>7,19; 11,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 18,69</t>
+          <t>13,04; 18,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 20,89</t>
+          <t>14,96; 20,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,04</t>
+          <t>15,53; 19,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,7</t>
+          <t>6,09; 8,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,07</t>
+          <t>9,54; 12,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 13,39</t>
+          <t>9,92; 13,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 15,38</t>
+          <t>12,58; 15,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,43</t>
+          <t>3,55; 6,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,71</t>
+          <t>5,22; 8,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,36</t>
+          <t>4,34; 7,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,37</t>
+          <t>5,29; 8,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,49</t>
+          <t>9,6; 13,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 18,15</t>
+          <t>13,55; 18,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 15,65</t>
+          <t>11,5; 15,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 20,07</t>
+          <t>15,9; 19,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,61</t>
+          <t>7,0; 9,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 12,81</t>
+          <t>9,77; 12,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,0</t>
+          <t>8,32; 11,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,8</t>
+          <t>10,89; 13,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,99</t>
+          <t>2,92; 5,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,61</t>
+          <t>3,74; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,3</t>
+          <t>4,71; 8,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,72</t>
+          <t>6,6; 10,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 14,63</t>
+          <t>10,04; 14,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,38; 17,79</t>
+          <t>12,47; 17,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,79</t>
+          <t>11,6; 16,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 16,51</t>
+          <t>13,42; 17,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,83</t>
+          <t>6,85; 9,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,98</t>
+          <t>8,7; 12,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 12,0</t>
+          <t>8,54; 11,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,8</t>
+          <t>10,62; 13,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,46</t>
+          <t>3,78; 6,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,66</t>
+          <t>5,94; 9,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,31</t>
+          <t>5,96; 9,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 12,17</t>
+          <t>8,1; 11,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,58</t>
+          <t>9,57; 13,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,42</t>
+          <t>13,87; 18,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,54</t>
+          <t>13,85; 18,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,32</t>
+          <t>16,61; 20,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 9,81</t>
+          <t>7,18; 9,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 13,79</t>
+          <t>10,59; 13,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 13,68</t>
+          <t>10,68; 13,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 15,83</t>
+          <t>13,0; 15,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,7</t>
+          <t>4,14; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,65</t>
+          <t>5,7; 7,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,09</t>
+          <t>5,51; 7,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,27</t>
+          <t>7,67; 9,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 12,09</t>
+          <t>10,14; 12,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,75</t>
+          <t>14,5; 16,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,94; 16,47</t>
+          <t>14,11; 16,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,22; 17,8</t>
+          <t>16,41; 18,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,75</t>
+          <t>7,44; 8,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,04</t>
+          <t>10,42; 11,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,54</t>
+          <t>10,04; 11,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>12,46; 13,88</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>70255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121213</t>
+          <t>129880</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>185390</t>
+          <t>200134</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28098; 50480</t>
+          <t>27186; 50552</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33237; 61878</t>
+          <t>33940; 61991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25517; 49620</t>
+          <t>25486; 48763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51505; 79436</t>
+          <t>56294; 88084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47995; 79342</t>
+          <t>49490; 78797</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91859; 130299</t>
+          <t>90884; 130008</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100436; 140572</t>
+          <t>100645; 138892</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93605; 138105</t>
+          <t>114020; 146230</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83681; 120295</t>
+          <t>84166; 123225</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133930; 183057</t>
+          <t>133667; 180665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132917; 180418</t>
+          <t>133713; 179726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>161238; 209322</t>
+          <t>179233; 222381</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64142</t>
+          <t>70343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>172290</t>
+          <t>189313</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>236432</t>
+          <t>259655</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34229; 61882</t>
+          <t>34181; 61572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54315; 88643</t>
+          <t>53178; 87237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44665; 75302</t>
+          <t>44411; 75158</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30901; 87876</t>
+          <t>55490; 87281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92432; 130682</t>
+          <t>93005; 133471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>139743; 187389</t>
+          <t>139834; 188250</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>119141; 163171</t>
+          <t>119910; 165709</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>154800; 192396</t>
+          <t>170377; 209021</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136699; 185508</t>
+          <t>135040; 184272</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>202198; 262658</t>
+          <t>200361; 260669</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172348; 227288</t>
+          <t>171857; 230904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163053; 275307</t>
+          <t>230963; 286388</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60568</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>194854</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18967; 40664</t>
+          <t>19787; 40559</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28724; 57673</t>
+          <t>28315; 58948</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35151; 63064</t>
+          <t>35745; 62961</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46327; 75528</t>
+          <t>52993; 85442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67813; 100056</t>
+          <t>68677; 101783</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96179; 138278</t>
+          <t>96915; 138017</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90912; 131827</t>
+          <t>91045; 131997</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54709; 154129</t>
+          <t>108984; 144207</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94501; 133926</t>
+          <t>93320; 134276</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133275; 183822</t>
+          <t>133565; 185307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134000; 185287</t>
+          <t>131857; 182486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>116034; 209691</t>
+          <t>171532; 221398</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>95904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>195123</t>
+          <t>207236</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>288838</t>
+          <t>303139</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35621; 60884</t>
+          <t>35616; 61012</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56626; 91536</t>
+          <t>56270; 92984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55541; 87295</t>
+          <t>55922; 89477</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77277; 112760</t>
+          <t>80177; 117212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>99944; 141073</t>
+          <t>99374; 140300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>145993; 193792</t>
+          <t>145902; 192174</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>144876; 193568</t>
+          <t>144606; 195651</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>160904; 222538</t>
+          <t>185923; 230348</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144754; 194276</t>
+          <t>142234; 193777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212931; 275850</t>
+          <t>211690; 270915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210591; 271030</t>
+          <t>211620; 269368</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>249431; 320066</t>
+          <t>274260; 331649</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>137711; 186644</t>
+          <t>135663; 187471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>198349; 262165</t>
+          <t>195270; 259956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184534; 240749</t>
+          <t>186862; 243370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222400; 320799</t>
+          <t>270968; 339187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>339971; 408540</t>
+          <t>342761; 412231</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>507726; 595880</t>
+          <t>515873; 602809</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>494082; 583729</t>
+          <t>500061; 586337</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>490632; 660644</t>
+          <t>613414; 689803</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>499543; 582131</t>
+          <t>495382; 586238</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>732170; 840872</t>
+          <t>727951; 834702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>699388; 800588</t>
+          <t>696469; 802855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>760517; 961645</t>
+          <t>906063; 1009350</t>
         </is>
       </c>
     </row>
